--- a/data/outputSpecialityRpt/File1/RPT_RPT4431929423193CE_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT4431929423193CE_outputSpecialityRpt.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -853,17 +853,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -877,51 +877,51 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0.1283543016797644</v>
+        <v>1.087706607086108</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>0.04260686221601883</v>
+        <v>1.117334332997156</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.03873188334745219</v>
+        <v>1.153908423304382</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.03493570552442494</v>
+        <v>1.180146651075024</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>0.03149004512659982</v>
+        <v>1.206155981008059</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$1027.4762369739342</t>
+          <t>$2677.439211535461</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$357.8882225541528</t>
+          <t>$2946.0045177576903</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$340.5798952855761</t>
+          <t>$3250.8061156854587</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$320.83451404919504</t>
+          <t>$3544.8399099043386</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$302.0615298407584</t>
+          <t>$3863.264531558746</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>50881001060</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1017,51 +1017,51 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.344926056939333</v>
+        <v>1.145849634121382</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.163279690102619</v>
+        <v>1.211582016299423</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>2.155507680301076</v>
+        <v>0.8273506247565391</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>2.248502802516199</v>
+        <v>0.5974401220671471</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>2.372296130820284</v>
+        <v>0.5975398073780157</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$21120.0</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$204692.7704102249</t>
+          <t>$24436.3323590373</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$135762.23092245893</t>
+          <t>$26035.57126577924</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$138716.2894239187</t>
+          <t>$17913.113466989635</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$148376.2592311176</t>
+          <t>$13032.404402543127</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$160539.67560417517</t>
+          <t>$13133.941904729345</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1157,51 +1157,51 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>1.710527744988765</v>
+        <v>3.263119821258325</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1.291723301176847</v>
+        <v>3.352002998991467</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.1750644499375648</v>
+        <v>3.461725269913147</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.0529844592780824</v>
+        <v>3.540439953225071</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>0.01733876873609616</v>
+        <v>3.618467943024177</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$5171.950990449212</t>
+          <t>$8095.773606514468</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$4138.776961984778</t>
+          <t>$8731.336851615144</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$592.2231114931147</t>
+          <t>$9466.321268716976</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$188.42051721501463</t>
+          <t>$10163.41526834504</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$64.82456869958668</t>
+          <t>$10905.62007741102</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1297,51 +1297,51 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>12.6043459753352</v>
+        <v>1.710527744988765</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>13.32740217929365</v>
+        <v>1.291723301176847</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>9.100856872321931</v>
+        <v>0.1750644499375648</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>6.571841342738619</v>
+        <v>0.0529844592780824</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>6.572937881158173</v>
+        <v>0.01733876873609616</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$293235.98830844765</t>
+          <t>$5171.9509904492115</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$312426.85518935084</t>
+          <t>$4138.776961984778</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$214957.36160387564</t>
+          <t>$592.2231114931147</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$156388.85283051748</t>
+          <t>$188.42051721501463</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$157607.30285675218</t>
+          <t>$64.82456869958668</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>50881001060</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1428,60 +1428,60 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I19" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>1.145849634121382</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>1.211582016299423</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.8273506247565391</v>
+        <v>0.455084237682646</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.5974401220671471</v>
+        <v>0.7501715529875564</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>0.5975398073780157</v>
+        <v>0.8206377504501495</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>$21120.0</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$24436.332359037307</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$26035.57126577924</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$17913.113466989635</t>
+          <t>$8870.890379522578</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$13032.404402543127</t>
+          <t>$14736.019856985533</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$13133.941904729345</t>
+          <t>$16244.834289904704</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,75 +1553,75 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1.087706607086108</v>
+        <v>1.757656948345875</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.117334332997156</v>
+        <v>1.748441604247599</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.153908423304382</v>
+        <v>1.747480134587764</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.180146651075024</v>
+        <v>1.733427959659759</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1.206155981008059</v>
+        <v>1.716482211696096</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$2677.4392115354613</t>
+          <t>$13000.494050692916</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$2946.0045177576903</t>
+          <t>$13527.996090287435</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$3250.8061156854587</t>
+          <t>$14145.31493205688</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$3544.8399099043386</t>
+          <t>$14707.607785162903</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$3863.264531558746</t>
+          <t>$15265.513526288303</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1717,51 +1717,51 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3.263119821258325</v>
+        <v>12.6043459753352</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>3.352002998991467</v>
+        <v>13.32740217929365</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>3.461725269913147</v>
+        <v>9.100856872321931</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.540439953225071</v>
+        <v>6.571841342738619</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>3.618467943024177</v>
+        <v>6.572937881158173</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$8095.77360651447</t>
+          <t>$293235.9883084476</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$8731.336851615144</t>
+          <t>$312426.85518935084</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$9466.321268716976</t>
+          <t>$214957.36160387564</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$10163.41526834504</t>
+          <t>$156388.85283051748</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$10905.62007741102</t>
+          <t>$157607.30285675218</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,125 +1833,125 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>3.136517305548107</v>
+        <v>2.402595122825411</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3.199215749149006</v>
+        <v>2.262179095563523</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>3.29162385491474</v>
+        <v>2.060556823882584</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>3.365249839644577</v>
+        <v>1.853753881321507</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>3.438169513775609</v>
+        <v>1.664790201106821</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$95113.78867480153</t>
+          <t>$17310.937970341267</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$99492.33717730765</t>
+          <t>$17104.55494124535</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$104970.65340268423</t>
+          <t>$16312.81569002672</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$110044.4407533169</t>
+          <t>$15330.385669803645</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$115297.68212605864</t>
+          <t>$14381.930699371356</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
         <is>
-          <t>$95113.78867480153</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V22" s="14" t="inlineStr">
         <is>
-          <t>$99492.33717730765</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W22" s="14" t="inlineStr">
         <is>
-          <t>$104970.65340268423</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X22" s="14" t="inlineStr">
         <is>
-          <t>$110044.4407533169</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y22" s="14" t="inlineStr">
         <is>
-          <t>$115297.68212605864</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z22" s="14" t="inlineStr">
         <is>
-          <t>$21971.939735797638</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA22" s="14" t="inlineStr">
         <is>
-          <t>$22411.155046961532</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB22" s="14" t="inlineStr">
         <is>
-          <t>$23058.492565996556</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC22" s="14" t="inlineStr">
         <is>
-          <t>$23574.257518611743</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD22" s="14" t="inlineStr">
         <is>
-          <t>$24085.074622259468</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>1.217626465453933</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>1.215670185123684</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>1.212574228326745</v>
+        <v>5.005926614509106</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>1.20596668031878</v>
+        <v>8.251887082863121</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>1.198574809183103</v>
+        <v>9.027015254951646</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$10006.015464766104</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$10449.154824197</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$10902.215591615217</t>
+          <t>$106450.68455427092</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$11362.714835636183</t>
+          <t>$176832.23828382636</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$11835.91154724438</t>
+          <t>$194938.01147885644</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2140,48 +2140,48 @@
         <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>3.270689785432134</v>
+        <v>0.1283543016797644</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>3.414630424282703</v>
+        <v>0.04260686221601883</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>3.564425520814865</v>
+        <v>0.03873188334745219</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>3.712898248811074</v>
+        <v>0.03493570552442494</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>3.864910242976473</v>
+        <v>0.03149004512659982</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$53231.07881215102</t>
+          <t>$1027.476236973934</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$58689.64164887507</t>
+          <t>$357.8882225541528</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$64693.46615682727</t>
+          <t>$340.5798952855761</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$71157.15040582666</t>
+          <t>$320.83451404919504</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$78222.00378075347</t>
+          <t>$302.0615298407584</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,125 +2253,125 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>2.402595122825411</v>
+        <v>3.136517305548107</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>2.262179095563523</v>
+        <v>3.199215749149006</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>2.060556823882584</v>
+        <v>3.29162385491474</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.853753881321507</v>
+        <v>3.365249839644577</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1.664790201106821</v>
+        <v>3.438169513775609</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$17310.937970341263</t>
+          <t>$95113.78867480152</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$17104.55494124535</t>
+          <t>$99492.33717730765</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$16312.81569002672</t>
+          <t>$104970.65340268423</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$15330.385669803645</t>
+          <t>$110044.4407533169</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$14381.930699371356</t>
+          <t>$115297.68212605864</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$95113.78867480152</t>
         </is>
       </c>
       <c r="V25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$99492.33717730765</t>
         </is>
       </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$104970.65340268423</t>
         </is>
       </c>
       <c r="X25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$110044.4407533169</t>
         </is>
       </c>
       <c r="Y25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$115297.68212605864</t>
         </is>
       </c>
       <c r="Z25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$21971.939735797638</t>
         </is>
       </c>
       <c r="AA25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$22411.155046961532</t>
         </is>
       </c>
       <c r="AB25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23058.492565996556</t>
         </is>
       </c>
       <c r="AC25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23574.257518611743</t>
         </is>
       </c>
       <c r="AD25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$24085.074622259468</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2408,60 +2408,60 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>1.22076901006598</v>
+        <v>3.344926056939333</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>2.635062791994738</v>
+        <v>2.163279690102619</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>2.955863352140419</v>
+        <v>2.155507680301076</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>3.139332955797313</v>
+        <v>2.248502802516199</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>3.300019600103826</v>
+        <v>2.372296130820284</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$67240.06568895873</t>
+          <t>$204692.77041022485</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$148858.6925393523</t>
+          <t>$135762.23092245893</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$171260.09591304994</t>
+          <t>$138716.2894239187</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$186551.09710359777</t>
+          <t>$148376.2592311176</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$201124.76331679616</t>
+          <t>$160539.67560417517</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
+        <v>1.22076901006598</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0.2673947790377587</v>
+        <v>2.635062791994737</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>1.22683710112138</v>
+        <v>2.955863352140419</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>1.206690781946901</v>
+        <v>3.139332955797313</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.113434018286723</v>
+        <v>3.300019600103827</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
@@ -2581,27 +2581,27 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$67240.06568895873</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$771.2095359422179</t>
+          <t>$148858.6925393523</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$3736.52791085084</t>
+          <t>$171260.09591304994</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$3864.2491842039617</t>
+          <t>$186551.09710359777</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$3749.051566979945</t>
+          <t>$201124.76331679616</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,75 +2673,75 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0</v>
+        <v>1.217626465453933</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>1.215670185123684</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>5.005926614509106</v>
+        <v>1.212574228326745</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>8.251887082863121</v>
+        <v>1.20596668031878</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>9.027015254951644</v>
+        <v>1.198574809183103</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10006.015464766102</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10449.154824197</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$106450.68455427092</t>
+          <t>$10902.215591615217</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$176832.23828382636</t>
+          <t>$11362.714835636183</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$194938.01147885644</t>
+          <t>$11835.91154724438</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,75 +2813,75 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0</v>
+        <v>3.270689785432134</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>0</v>
+        <v>3.414630424282703</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.4550842376826459</v>
+        <v>3.564425520814865</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.7501715529875564</v>
+        <v>3.712898248811074</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>0.8206377504501494</v>
+        <v>3.864910242976473</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$53231.078812151005</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$58689.64164887507</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$8870.890379522578</t>
+          <t>$64693.46615682727</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$14736.019856985533</t>
+          <t>$71157.15040582666</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$16244.834289904704</t>
+          <t>$78222.00378075347</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2980,19 +2980,19 @@
         <v>0</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.757656948345875</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.748441604247599</v>
+        <v>0.2673947790377587</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1.747480134587764</v>
+        <v>1.22683710112138</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>1.733427959659759</v>
+        <v>1.206690781946901</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1.716482211696096</v>
+        <v>1.113434018286723</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
@@ -3001,27 +3001,27 @@
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$13000.494050692914</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$13527.996090287435</t>
+          <t>$771.2095359422179</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$14145.31493205688</t>
+          <t>$3736.52791085084</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$14707.607785162903</t>
+          <t>$3864.2491842039617</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$15265.513526288303</t>
+          <t>$3749.051566979945</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
